--- a/test_member.xlsx
+++ b/test_member.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,151 +425,151 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC4"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>DOB</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Gender</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Email</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Phone</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>PCPID</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>PlanID</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ZIP</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>ChronicConditions</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>InsuranceType</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>EnrollmentStart</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>EnrollmentEnd</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PriorScreenings</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>HeightCm</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>WeightKg</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>SmokingStatus</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>AlcoholUse</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>ExerciseFrequency</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DietType</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SleepHoursAvg</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>StressLevel</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>LifestyleNotes</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>FamilyHistory</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>PastConditions</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>CurrentConditions</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Surgeries</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Allergies</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Medications</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Immunizations</t>
         </is>
@@ -566,12 +578,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Priya Raman</t>
+          <t>Jennifer Walker</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1968-03-12</t>
+          <t>1958-04-12</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -586,7 +598,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>+15551110001</t>
+          <t>15552220001</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -604,19 +616,15 @@
           <t>10001</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Type 2 Diabetes, Hypertension</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Commercial</t>
+          <t>Medicare</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -624,16 +632,12 @@
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>BCS:2023-07-10</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O2" t="n">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
@@ -647,57 +651,45 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1-2x/week</t>
+          <t>2-3x/week</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>High-sodium</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Recent weight gain post-retirement.</t>
+          <t>Retired school teacher.</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>father|false|72|Colorectal Cancer,Diabetes Type 2;mother|true|70|Hypertension;sibling|true|52|Breast Cancer</t>
+          <t>mother|false|68|Breast Cancer;sibling|true|54|Hypertension</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Bronchitis|2018|resolved;Migraine|2012|resolved</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Hypertension|2019;Type 2 Diabetes|2021</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Appendectomy|2005</t>
-        </is>
-      </c>
+          <t>Bronchitis|2015|resolved</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
           <t>Penicillin|moderate|rash</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Metformin|500mg BID|2021|Diabetes;Lisinopril|10mg|2019|BP control</t>
-        </is>
-      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>Influenza|2025;Tdap|2020</t>
@@ -707,17 +699,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>David Chen</t>
+          <t>Linda Johnson</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1975-09-04</t>
+          <t>1962-07-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -727,7 +719,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>+15551110002</t>
+          <t>15552220002</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -745,11 +737,7 @@
           <t>60614</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>High Cholesterol</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>Commercial</t>
@@ -757,7 +745,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -767,33 +755,33 @@
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="O3" t="n">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Never</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>None</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>Sedentary</t>
+          <t>1-2x/week</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>Fast-food-heavy</t>
+          <t>High-sodium</t>
         </is>
       </c>
       <c r="T3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -802,46 +790,42 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Desk job, travels frequently.</t>
+          <t>Office manager, sedentary.</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>father|false|64|Coronary Artery Disease,Stroke;mother|true|72|Hypertension;sibling|true|48|Diabetes Type 2</t>
+          <t>mother|true|82|Hypertension;father|false|79|Heart Disease</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>High Cholesterol|2022</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Knee arthroscopy|2019</t>
-        </is>
-      </c>
+          <t>Hypertension|2020</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>Atorvastatin|20mg|2022|Cholesterol</t>
+          <t>Lisinopril|10mg|2020|BP control</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>COVID-19|2023;Influenza|2024</t>
+          <t>Influenza|2025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Maria Gonzalez</t>
+          <t>Patricia Miller</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1955-11-20</t>
+          <t>1954-11-03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -856,7 +840,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>+15551110003</t>
+          <t>15552220003</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -882,7 +866,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -890,16 +874,12 @@
           <t>2026-12-31</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>COL:2022-04-11;BCS:2024-09-05</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>158</v>
       </c>
       <c r="O4" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
@@ -908,7 +888,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Occasional</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -931,30 +911,877 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Active retiree, walks 5km daily.</t>
+          <t>Active retiree, walks daily.</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>mother|false|74|Breast Cancer;father|false|80|Heart Disease;sibling|true|68|Hypertension</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>Anemia|2016|resolved</t>
-        </is>
-      </c>
+          <t>sibling|true|70|Osteoporosis</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>Pollen|mild|sneezing</t>
-        </is>
-      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Cataract surgery|2023</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Influenza|2025;Pneumococcal|2023;Shingles|2021</t>
+          <t>Influenza|2025;Shingles|2021;Pneumococcal|2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Barbara Davis</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1967-02-18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ajohnsm2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>15552220004</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>P1000</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>PLAN-001</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>94103</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="n">
+        <v>168</v>
+      </c>
+      <c r="O5" t="n">
+        <v>82</v>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Former</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Fast-food-heavy</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
+        <v>5</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>High-stress corporate role.</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>mother|false|71|Breast Cancer;father|true|75|Diabetes Type 2</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Anemia|2018|resolved</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>High Cholesterol|2023</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Latex|mild|skin rash</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Atorvastatin|20mg|2023|Cholesterol</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Influenza|2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Susan Wilson</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1970-09-09</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ajohnsm2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>15552220005</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>P1000</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>PLAN-001</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>75201</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="n">
+        <v>163</v>
+      </c>
+      <c r="O6" t="n">
+        <v>70</v>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Occasional</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>2-3x/week</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Balanced</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>7</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Nurse, regular checkups.</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>sibling|true|58|Type 2 Diabetes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Appendectomy|2010</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Influenza|2025;Tdap|2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Mary Thompson</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1952-06-30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ajohnsm2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>15552220006</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>P1000</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>PLAN-001</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>02108</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="n">
+        <v>157</v>
+      </c>
+      <c r="O7" t="n">
+        <v>68</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Former</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Low-fat</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gardener, very active.</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>mother|false|78|Stroke</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Hypothyroidism|2005|managed</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Hypothyroidism|2005</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Levothyroxine|50mcg|2005|Thyroid</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Influenza|2025;Shingles|2019;Pneumococcal|2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Karen Anderson</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1965-12-14</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ajohnsm2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15552220007</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>P1000</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>PLAN-001</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>30303</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="n">
+        <v>170</v>
+      </c>
+      <c r="O8" t="n">
+        <v>88</v>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Current</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>Sedentary</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>High-carb</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Smoker, trying to quit.</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>father|false|69|Lung Cancer;mother|true|74|Hypertension</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Hypertension|2022</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>Amlodipine|5mg|2022|BP control</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Influenza|2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Nancy Martinez</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1960-03-22</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>ajohnsm2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15552220008</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>P1000</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>PLAN-001</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>85001</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="n">
+        <v>161</v>
+      </c>
+      <c r="O9" t="n">
+        <v>74</v>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Occasional</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>3-4x/week</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>Mediterranean</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
+        <v>7</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Yoga instructor.</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>sibling|false|62|Breast Cancer</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Migraine|2000|resolved</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Shellfish|severe|anaphylaxis</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Influenza|2025;Tdap|2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Betty Robinson</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1956-08-07</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ajohnsm2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>15552220009</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>P1000</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>PLAN-001</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>19103</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Medicare</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="n">
+        <v>159</v>
+      </c>
+      <c r="O10" t="n">
+        <v>71</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Former</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1-2x/week</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>Balanced</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>7</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Volunteer librarian.</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>mother|false|80|Osteoporosis;father|false|76|Prostate Cancer</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Osteopenia|2020</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Hysterectomy|2008</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>Calcium+D|600mg|2020|Bone health</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Influenza|2025;Shingles|2020</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Sandra Clark</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1972-05-16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ajohnsm2020@gmail.com</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15552220010</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>P1000</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>PLAN-001</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>98101</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Commercial</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2024-01-01</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-12-31</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="n">
+        <v>166</v>
+      </c>
+      <c r="O11" t="n">
+        <v>76</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Never</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Occasional</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2-3x/week</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>Balanced</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>7</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Software project manager.</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>mother|true|76|Hypertension</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Influenza|2025;Tdap|2023</t>
         </is>
       </c>
     </row>
